--- a/output/pdf_financials_xlsx/FROG.xlsx
+++ b/output/pdf_financials_xlsx/FROG.xlsx
@@ -678,10 +678,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.00092</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.00035</v>
       </c>
     </row>
     <row r="13">
@@ -1030,10 +1030,10 @@
         <v>-0.097224</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.7870549999999999</v>
+        <v>-0.787975</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.685013</v>
+        <v>-0.6853630000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1074,10 +1074,10 @@
         <v>-0.097224</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.78588</v>
+        <v>-0.7868000000000001</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.680204</v>
+        <v>-0.680554</v>
       </c>
     </row>
     <row r="30">
@@ -1192,7 +1192,7 @@
         <v>0.03409</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.007259</v>
       </c>
     </row>
     <row r="35">
@@ -1236,7 +1236,7 @@
         <v>0.03409</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.007259</v>
       </c>
     </row>
     <row r="37">
@@ -1500,7 +1500,7 @@
         <v>0.015665</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.066623</v>
+        <v>0.059364</v>
       </c>
     </row>
     <row r="49">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">

--- a/output/pdf_financials_xlsx/FROG.xlsx
+++ b/output/pdf_financials_xlsx/FROG.xlsx
@@ -1920,19 +1920,19 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.0105</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.0125</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="68">
@@ -2910,7 +2910,7 @@
         <v>0</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.023491</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>0</v>
@@ -3426,7 +3426,7 @@
         <v>0</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.023491</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>0</v>
@@ -3448,7 +3448,7 @@
         <v>-0.102243</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.689765</v>
+        <v>-0.713256</v>
       </c>
       <c r="F135" s="3" t="n">
         <v>-0.64913</v>
@@ -6103,7 +6103,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -7909,7 +7913,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E110" s="5" t="n">
         <v>-0.003042</v>
       </c>
